--- a/Dades3/154_SEQ_BP/154_MasterFile.xlsx
+++ b/Dades3/154_SEQ_BP/154_MasterFile.xlsx
@@ -469,7 +469,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5">
@@ -61965,7 +61965,6 @@
       <c r="A2" t="n">
         <v>8</v>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="D2" t="n">
         <v>0</v>
       </c>
@@ -61974,7 +61973,6 @@
       <c r="A3" t="n">
         <v>9</v>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="D3" t="n">
         <v>0</v>
       </c>
@@ -61983,7 +61981,6 @@
       <c r="A4" t="n">
         <v>10</v>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="D4" t="n">
         <v>0</v>
       </c>
@@ -61992,7 +61989,6 @@
       <c r="A5" t="n">
         <v>11</v>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="D5" t="n">
         <v>0</v>
       </c>
@@ -62001,7 +61997,6 @@
       <c r="A6" t="n">
         <v>12</v>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="D6" t="n">
         <v>0</v>
       </c>
@@ -62010,7 +62005,6 @@
       <c r="A7" t="n">
         <v>13</v>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="D7" t="n">
         <v>0</v>
       </c>
@@ -62019,7 +62013,6 @@
       <c r="A8" t="n">
         <v>14</v>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="D8" t="n">
         <v>0</v>
       </c>
@@ -62028,7 +62021,6 @@
       <c r="A9" t="n">
         <v>15</v>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="D9" t="n">
         <v>0</v>
       </c>
@@ -62037,7 +62029,6 @@
       <c r="A10" t="n">
         <v>16</v>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="D10" t="n">
         <v>0</v>
       </c>
@@ -62046,7 +62037,6 @@
       <c r="A11" t="n">
         <v>17</v>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="D11" t="n">
         <v>0</v>
       </c>
@@ -62055,7 +62045,6 @@
       <c r="A12" t="n">
         <v>18</v>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="D12" t="n">
         <v>0</v>
       </c>
@@ -62064,7 +62053,6 @@
       <c r="A13" t="n">
         <v>19</v>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="D13" t="n">
         <v>0</v>
       </c>
@@ -62073,7 +62061,6 @@
       <c r="A14" t="n">
         <v>20</v>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="D14" t="n">
         <v>0</v>
       </c>
@@ -62082,7 +62069,6 @@
       <c r="A15" t="n">
         <v>21</v>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="D15" t="n">
         <v>0</v>
       </c>
@@ -62091,7 +62077,6 @@
       <c r="A16" t="n">
         <v>22</v>
       </c>
-      <c r="B16" t="inlineStr"/>
       <c r="D16" t="n">
         <v>0</v>
       </c>
@@ -62100,7 +62085,6 @@
       <c r="A17" t="n">
         <v>23</v>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="D17" t="n">
         <v>0</v>
       </c>
@@ -62109,7 +62093,6 @@
       <c r="A18" t="n">
         <v>24</v>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="D18" t="n">
         <v>0</v>
       </c>
@@ -62118,7 +62101,6 @@
       <c r="A19" t="n">
         <v>25</v>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="D19" t="n">
         <v>0</v>
       </c>
@@ -62127,7 +62109,6 @@
       <c r="A20" t="n">
         <v>26</v>
       </c>
-      <c r="B20" t="inlineStr"/>
       <c r="D20" t="n">
         <v>0</v>
       </c>
@@ -62136,7 +62117,6 @@
       <c r="A21" t="n">
         <v>27</v>
       </c>
-      <c r="B21" t="inlineStr"/>
       <c r="D21" t="n">
         <v>0</v>
       </c>
@@ -62145,7 +62125,6 @@
       <c r="A22" t="n">
         <v>28</v>
       </c>
-      <c r="B22" t="inlineStr"/>
       <c r="D22" t="n">
         <v>0</v>
       </c>
@@ -62154,7 +62133,6 @@
       <c r="A23" t="n">
         <v>29</v>
       </c>
-      <c r="B23" t="inlineStr"/>
       <c r="D23" t="n">
         <v>0</v>
       </c>
@@ -62163,7 +62141,6 @@
       <c r="A24" t="n">
         <v>30</v>
       </c>
-      <c r="B24" t="inlineStr"/>
       <c r="D24" t="n">
         <v>0</v>
       </c>
@@ -62172,7 +62149,6 @@
       <c r="A25" t="n">
         <v>31</v>
       </c>
-      <c r="B25" t="inlineStr"/>
       <c r="D25" t="n">
         <v>0</v>
       </c>
@@ -62181,7 +62157,6 @@
       <c r="A26" t="n">
         <v>32</v>
       </c>
-      <c r="B26" t="inlineStr"/>
       <c r="D26" t="n">
         <v>0</v>
       </c>
@@ -62190,7 +62165,6 @@
       <c r="A27" t="n">
         <v>33</v>
       </c>
-      <c r="B27" t="inlineStr"/>
       <c r="D27" t="n">
         <v>0</v>
       </c>
@@ -62199,7 +62173,6 @@
       <c r="A28" t="n">
         <v>34</v>
       </c>
-      <c r="B28" t="inlineStr"/>
       <c r="D28" t="n">
         <v>0</v>
       </c>
@@ -62208,7 +62181,6 @@
       <c r="A29" t="n">
         <v>35</v>
       </c>
-      <c r="B29" t="inlineStr"/>
       <c r="D29" t="n">
         <v>0</v>
       </c>
@@ -62217,7 +62189,6 @@
       <c r="A30" t="n">
         <v>36</v>
       </c>
-      <c r="B30" t="inlineStr"/>
       <c r="D30" t="n">
         <v>0</v>
       </c>
@@ -62226,7 +62197,6 @@
       <c r="A31" t="n">
         <v>37</v>
       </c>
-      <c r="B31" t="inlineStr"/>
       <c r="D31" t="n">
         <v>0</v>
       </c>
@@ -62235,7 +62205,6 @@
       <c r="A32" t="n">
         <v>38</v>
       </c>
-      <c r="B32" t="inlineStr"/>
       <c r="D32" t="n">
         <v>0</v>
       </c>
@@ -62244,7 +62213,6 @@
       <c r="A33" t="n">
         <v>39</v>
       </c>
-      <c r="B33" t="inlineStr"/>
       <c r="D33" t="n">
         <v>0</v>
       </c>
@@ -62253,7 +62221,6 @@
       <c r="A34" t="n">
         <v>40</v>
       </c>
-      <c r="B34" t="inlineStr"/>
       <c r="D34" t="n">
         <v>0</v>
       </c>
@@ -62262,7 +62229,6 @@
       <c r="A35" t="n">
         <v>41</v>
       </c>
-      <c r="B35" t="inlineStr"/>
       <c r="D35" t="n">
         <v>0</v>
       </c>
@@ -62271,7 +62237,6 @@
       <c r="A36" t="n">
         <v>42</v>
       </c>
-      <c r="B36" t="inlineStr"/>
       <c r="D36" t="n">
         <v>0</v>
       </c>
@@ -62280,7 +62245,6 @@
       <c r="A37" t="n">
         <v>43</v>
       </c>
-      <c r="B37" t="inlineStr"/>
       <c r="D37" t="n">
         <v>0</v>
       </c>
@@ -62289,7 +62253,6 @@
       <c r="A38" t="n">
         <v>44</v>
       </c>
-      <c r="B38" t="inlineStr"/>
       <c r="D38" t="n">
         <v>0</v>
       </c>
@@ -62298,7 +62261,6 @@
       <c r="A39" t="n">
         <v>45</v>
       </c>
-      <c r="B39" t="inlineStr"/>
       <c r="D39" t="n">
         <v>0</v>
       </c>
@@ -62307,7 +62269,6 @@
       <c r="A40" t="n">
         <v>46</v>
       </c>
-      <c r="B40" t="inlineStr"/>
       <c r="D40" t="n">
         <v>0</v>
       </c>
@@ -62316,7 +62277,6 @@
       <c r="A41" t="n">
         <v>47</v>
       </c>
-      <c r="B41" t="inlineStr"/>
       <c r="D41" t="n">
         <v>0</v>
       </c>
@@ -62325,7 +62285,6 @@
       <c r="A42" t="n">
         <v>48</v>
       </c>
-      <c r="B42" t="inlineStr"/>
       <c r="D42" t="n">
         <v>0</v>
       </c>
@@ -62334,7 +62293,6 @@
       <c r="A43" t="n">
         <v>49</v>
       </c>
-      <c r="B43" t="inlineStr"/>
       <c r="D43" t="n">
         <v>0</v>
       </c>
@@ -62343,7 +62301,6 @@
       <c r="A44" t="n">
         <v>50</v>
       </c>
-      <c r="B44" t="inlineStr"/>
       <c r="D44" t="n">
         <v>0</v>
       </c>
@@ -62352,7 +62309,6 @@
       <c r="A45" t="n">
         <v>51</v>
       </c>
-      <c r="B45" t="inlineStr"/>
       <c r="D45" t="n">
         <v>0</v>
       </c>
@@ -62361,7 +62317,6 @@
       <c r="A46" t="n">
         <v>52</v>
       </c>
-      <c r="B46" t="inlineStr"/>
       <c r="D46" t="n">
         <v>0</v>
       </c>
@@ -62370,7 +62325,6 @@
       <c r="A47" t="n">
         <v>53</v>
       </c>
-      <c r="B47" t="inlineStr"/>
       <c r="D47" t="n">
         <v>0</v>
       </c>
@@ -62379,7 +62333,6 @@
       <c r="A48" t="n">
         <v>54</v>
       </c>
-      <c r="B48" t="inlineStr"/>
       <c r="D48" t="n">
         <v>0</v>
       </c>
@@ -62388,7 +62341,6 @@
       <c r="A49" t="n">
         <v>55</v>
       </c>
-      <c r="B49" t="inlineStr"/>
       <c r="D49" t="n">
         <v>0</v>
       </c>
@@ -62397,7 +62349,6 @@
       <c r="A50" t="n">
         <v>56</v>
       </c>
-      <c r="B50" t="inlineStr"/>
       <c r="D50" t="n">
         <v>0</v>
       </c>
@@ -62406,7 +62357,6 @@
       <c r="A51" t="n">
         <v>57</v>
       </c>
-      <c r="B51" t="inlineStr"/>
       <c r="D51" t="n">
         <v>0</v>
       </c>
@@ -62415,7 +62365,6 @@
       <c r="A52" t="n">
         <v>58</v>
       </c>
-      <c r="B52" t="inlineStr"/>
       <c r="D52" t="n">
         <v>0</v>
       </c>
@@ -62424,7 +62373,6 @@
       <c r="A53" t="n">
         <v>59</v>
       </c>
-      <c r="B53" t="inlineStr"/>
       <c r="D53" t="n">
         <v>0</v>
       </c>
@@ -62433,7 +62381,6 @@
       <c r="A54" t="n">
         <v>60</v>
       </c>
-      <c r="B54" t="inlineStr"/>
       <c r="D54" t="n">
         <v>0</v>
       </c>
@@ -62442,7 +62389,6 @@
       <c r="A55" t="n">
         <v>61</v>
       </c>
-      <c r="B55" t="inlineStr"/>
       <c r="D55" t="n">
         <v>0</v>
       </c>
@@ -62451,7 +62397,6 @@
       <c r="A56" t="n">
         <v>62</v>
       </c>
-      <c r="B56" t="inlineStr"/>
       <c r="D56" t="n">
         <v>0</v>
       </c>
@@ -62460,7 +62405,6 @@
       <c r="A57" t="n">
         <v>63</v>
       </c>
-      <c r="B57" t="inlineStr"/>
       <c r="D57" t="n">
         <v>0</v>
       </c>
@@ -62469,7 +62413,6 @@
       <c r="A58" t="n">
         <v>64</v>
       </c>
-      <c r="B58" t="inlineStr"/>
       <c r="D58" t="n">
         <v>0</v>
       </c>
@@ -62478,7 +62421,6 @@
       <c r="A59" t="n">
         <v>65</v>
       </c>
-      <c r="B59" t="inlineStr"/>
       <c r="D59" t="n">
         <v>0</v>
       </c>
@@ -62487,7 +62429,6 @@
       <c r="A60" t="n">
         <v>66</v>
       </c>
-      <c r="B60" t="inlineStr"/>
       <c r="D60" t="n">
         <v>0</v>
       </c>
@@ -62496,7 +62437,6 @@
       <c r="A61" t="n">
         <v>67</v>
       </c>
-      <c r="B61" t="inlineStr"/>
       <c r="D61" t="n">
         <v>0</v>
       </c>
@@ -62505,7 +62445,6 @@
       <c r="A62" t="n">
         <v>68</v>
       </c>
-      <c r="B62" t="inlineStr"/>
       <c r="D62" t="n">
         <v>0</v>
       </c>
@@ -62514,7 +62453,6 @@
       <c r="A63" t="n">
         <v>69</v>
       </c>
-      <c r="B63" t="inlineStr"/>
       <c r="D63" t="n">
         <v>0</v>
       </c>
@@ -62523,7 +62461,6 @@
       <c r="A64" t="n">
         <v>70</v>
       </c>
-      <c r="B64" t="inlineStr"/>
       <c r="D64" t="n">
         <v>0</v>
       </c>
@@ -62532,7 +62469,6 @@
       <c r="A65" t="n">
         <v>71</v>
       </c>
-      <c r="B65" t="inlineStr"/>
       <c r="D65" t="n">
         <v>0</v>
       </c>
@@ -62541,7 +62477,6 @@
       <c r="A66" t="n">
         <v>72</v>
       </c>
-      <c r="B66" t="inlineStr"/>
       <c r="D66" t="n">
         <v>0</v>
       </c>
@@ -62550,7 +62485,6 @@
       <c r="A67" t="n">
         <v>73</v>
       </c>
-      <c r="B67" t="inlineStr"/>
       <c r="D67" t="n">
         <v>0</v>
       </c>
@@ -62559,7 +62493,6 @@
       <c r="A68" t="n">
         <v>74</v>
       </c>
-      <c r="B68" t="inlineStr"/>
       <c r="D68" t="n">
         <v>0</v>
       </c>
@@ -62568,7 +62501,6 @@
       <c r="A69" t="n">
         <v>75</v>
       </c>
-      <c r="B69" t="inlineStr"/>
       <c r="D69" t="n">
         <v>0</v>
       </c>
@@ -62577,7 +62509,6 @@
       <c r="A70" t="n">
         <v>76</v>
       </c>
-      <c r="B70" t="inlineStr"/>
       <c r="D70" t="n">
         <v>0</v>
       </c>
@@ -62586,7 +62517,6 @@
       <c r="A71" t="n">
         <v>77</v>
       </c>
-      <c r="B71" t="inlineStr"/>
       <c r="D71" t="n">
         <v>0</v>
       </c>
@@ -62595,7 +62525,6 @@
       <c r="A72" t="n">
         <v>78</v>
       </c>
-      <c r="B72" t="inlineStr"/>
       <c r="D72" t="n">
         <v>0</v>
       </c>
@@ -62604,7 +62533,6 @@
       <c r="A73" t="n">
         <v>79</v>
       </c>
-      <c r="B73" t="inlineStr"/>
       <c r="D73" t="n">
         <v>0</v>
       </c>
@@ -62613,7 +62541,6 @@
       <c r="A74" t="n">
         <v>80</v>
       </c>
-      <c r="B74" t="inlineStr"/>
       <c r="D74" t="n">
         <v>0</v>
       </c>
@@ -62622,7 +62549,6 @@
       <c r="A75" t="n">
         <v>81</v>
       </c>
-      <c r="B75" t="inlineStr"/>
       <c r="D75" t="n">
         <v>0</v>
       </c>
@@ -62631,7 +62557,6 @@
       <c r="A76" t="n">
         <v>82</v>
       </c>
-      <c r="B76" t="inlineStr"/>
       <c r="D76" t="n">
         <v>0</v>
       </c>
@@ -62640,7 +62565,6 @@
       <c r="A77" t="n">
         <v>83</v>
       </c>
-      <c r="B77" t="inlineStr"/>
       <c r="D77" t="n">
         <v>0</v>
       </c>
@@ -62649,7 +62573,6 @@
       <c r="A78" t="n">
         <v>84</v>
       </c>
-      <c r="B78" t="inlineStr"/>
       <c r="D78" t="n">
         <v>0</v>
       </c>
@@ -62658,7 +62581,6 @@
       <c r="A79" t="n">
         <v>85</v>
       </c>
-      <c r="B79" t="inlineStr"/>
       <c r="D79" t="n">
         <v>0</v>
       </c>
@@ -62667,7 +62589,6 @@
       <c r="A80" t="n">
         <v>86</v>
       </c>
-      <c r="B80" t="inlineStr"/>
       <c r="D80" t="n">
         <v>0</v>
       </c>
@@ -62676,7 +62597,6 @@
       <c r="A81" t="n">
         <v>87</v>
       </c>
-      <c r="B81" t="inlineStr"/>
       <c r="D81" t="n">
         <v>0</v>
       </c>
@@ -62685,7 +62605,6 @@
       <c r="A82" t="n">
         <v>88</v>
       </c>
-      <c r="B82" t="inlineStr"/>
       <c r="D82" t="n">
         <v>0</v>
       </c>
@@ -62694,7 +62613,6 @@
       <c r="A83" t="n">
         <v>89</v>
       </c>
-      <c r="B83" t="inlineStr"/>
       <c r="D83" t="n">
         <v>0</v>
       </c>
@@ -62703,7 +62621,6 @@
       <c r="A84" t="n">
         <v>90</v>
       </c>
-      <c r="B84" t="inlineStr"/>
       <c r="D84" t="n">
         <v>0</v>
       </c>
@@ -62712,7 +62629,6 @@
       <c r="A85" t="n">
         <v>91</v>
       </c>
-      <c r="B85" t="inlineStr"/>
       <c r="D85" t="n">
         <v>0</v>
       </c>
@@ -62721,7 +62637,6 @@
       <c r="A86" t="n">
         <v>92</v>
       </c>
-      <c r="B86" t="inlineStr"/>
       <c r="D86" t="n">
         <v>0</v>
       </c>
@@ -62730,7 +62645,6 @@
       <c r="A87" t="n">
         <v>93</v>
       </c>
-      <c r="B87" t="inlineStr"/>
       <c r="D87" t="n">
         <v>0</v>
       </c>
@@ -62739,7 +62653,6 @@
       <c r="A88" t="n">
         <v>94</v>
       </c>
-      <c r="B88" t="inlineStr"/>
       <c r="D88" t="n">
         <v>0</v>
       </c>
@@ -62748,7 +62661,6 @@
       <c r="A89" t="n">
         <v>95</v>
       </c>
-      <c r="B89" t="inlineStr"/>
       <c r="D89" t="n">
         <v>0</v>
       </c>
@@ -62757,7 +62669,6 @@
       <c r="A90" t="n">
         <v>96</v>
       </c>
-      <c r="B90" t="inlineStr"/>
       <c r="D90" t="n">
         <v>0</v>
       </c>
@@ -62766,7 +62677,6 @@
       <c r="A91" t="n">
         <v>97</v>
       </c>
-      <c r="B91" t="inlineStr"/>
       <c r="D91" t="n">
         <v>0</v>
       </c>
@@ -62775,7 +62685,6 @@
       <c r="A92" t="n">
         <v>98</v>
       </c>
-      <c r="B92" t="inlineStr"/>
       <c r="D92" t="n">
         <v>0</v>
       </c>
@@ -62784,7 +62693,6 @@
       <c r="A93" t="n">
         <v>99</v>
       </c>
-      <c r="B93" t="inlineStr"/>
       <c r="D93" t="n">
         <v>0</v>
       </c>
@@ -62793,7 +62701,6 @@
       <c r="A94" t="n">
         <v>100</v>
       </c>
-      <c r="B94" t="inlineStr"/>
       <c r="D94" t="n">
         <v>0</v>
       </c>
@@ -62802,7 +62709,6 @@
       <c r="A95" t="n">
         <v>101</v>
       </c>
-      <c r="B95" t="inlineStr"/>
       <c r="D95" t="n">
         <v>0</v>
       </c>
@@ -62811,7 +62717,6 @@
       <c r="A96" t="n">
         <v>102</v>
       </c>
-      <c r="B96" t="inlineStr"/>
       <c r="D96" t="n">
         <v>0</v>
       </c>
@@ -62820,7 +62725,6 @@
       <c r="A97" t="n">
         <v>103</v>
       </c>
-      <c r="B97" t="inlineStr"/>
       <c r="D97" t="n">
         <v>0</v>
       </c>
@@ -62829,7 +62733,6 @@
       <c r="A98" t="n">
         <v>104</v>
       </c>
-      <c r="B98" t="inlineStr"/>
       <c r="D98" t="n">
         <v>0</v>
       </c>
@@ -62838,7 +62741,6 @@
       <c r="A99" t="n">
         <v>105</v>
       </c>
-      <c r="B99" t="inlineStr"/>
       <c r="D99" t="n">
         <v>0</v>
       </c>
@@ -62847,7 +62749,6 @@
       <c r="A100" t="n">
         <v>106</v>
       </c>
-      <c r="B100" t="inlineStr"/>
       <c r="D100" t="n">
         <v>0</v>
       </c>
